--- a/画面レイアウト図 ログイン.xlsx
+++ b/画面レイアウト図 ログイン.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER110\Desktop\プロジェクト演習\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER110\Documents\TasBo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813BFA30-EFAA-45CC-84BA-970AB398A385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{330B9D69-64B6-4BB9-82E8-0D82FE3FCE26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DB71744D-6536-499F-BA61-C37DA65DFC77}"/>
   </bookViews>
@@ -96,10 +96,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>チームTanBo</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>菊地</t>
     <rPh sb="0" eb="2">
       <t>キクチ</t>
@@ -148,6 +144,10 @@
   </si>
   <si>
     <t>submit</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チームTasBo</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -633,6 +633,114 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -642,127 +750,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1651,380 +1651,363 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4" t="s">
+      <c r="B1" s="38"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="4" t="s">
+      <c r="E1" s="28"/>
+      <c r="F1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="6" t="s">
+      <c r="G1" s="28"/>
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="9"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="12" t="s">
+      <c r="A2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="13"/>
-      <c r="F2" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="13"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="43"/>
       <c r="H2" s="45">
         <v>46175</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="24"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="34"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="25"/>
+    </row>
+    <row r="4" spans="1:10" ht="19.5" thickBot="1">
+      <c r="A4" s="34"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="25"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="27"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="15"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="9"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="18"/>
-    </row>
-    <row r="4" spans="1:10" ht="19.5" thickBot="1">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="18"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="21" t="s">
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="30"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="14"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="31"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="33"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="34"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="36"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="34"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="36"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="34"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="36"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="34"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="36"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="34"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="36"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="34"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="36"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="25"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="26"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="28"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="29"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="29"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="29"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="9"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="29"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="9"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="29"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="29"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="25"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="31" t="s">
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="J15" s="33" t="s">
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="11"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="10">
+        <v>1</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" s="24"/>
-      <c r="J16" s="25"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="35">
-        <v>1</v>
-      </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="36" t="s">
+      <c r="F17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="7"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="10">
+        <v>2</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="7"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="10">
+        <v>3</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" s="37" t="s">
+      <c r="F19" s="7"/>
+      <c r="G19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="13"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="10">
+        <v>4</v>
+      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G17" s="37"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="25"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="35">
-        <v>2</v>
-      </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="G18" s="37"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="25"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="35">
-        <v>3</v>
-      </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="31"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="25"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="35">
-        <v>4</v>
-      </c>
-      <c r="B20" s="24"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="36" t="s">
+      <c r="E20" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="H20" s="31"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="25"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="13"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="14"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="35"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="25"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="14"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="35"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="25"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="14"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" thickBot="1">
-      <c r="A23" s="38"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="44"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -2039,6 +2022,23 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
